--- a/data/awsdata.xlsx
+++ b/data/awsdata.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\My PC\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\My PC\OneDrive\Documents\Data_Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F9269F-AAD4-4FFC-8D17-D8D0B3CFB8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E84BA5-9A45-4507-B07B-617E057041C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{21FCFC82-A5BA-4553-89C8-76720EB0878F}"/>
   </bookViews>
   <sheets>
-    <sheet name="September" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">September!$A$1:$E$497</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$E$466</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="14">
   <si>
     <t>StationID</t>
   </si>
@@ -73,9 +73,6 @@
   </si>
   <si>
     <t>WindDirectionAVG</t>
-  </si>
-  <si>
-    <t>ApoeraAWS</t>
   </si>
   <si>
     <t>EAGAWS</t>
@@ -628,9 +625,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -668,7 +665,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -774,7 +771,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -916,7 +913,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -924,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{593AC91C-CFC4-433E-83EC-9477B450705E}">
-  <dimension ref="A1:K497"/>
+  <dimension ref="A1:K466"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
@@ -977,67 +974,104 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="E2" s="1">
+        <v>25.602898550724642</v>
+      </c>
+      <c r="F2" s="1">
+        <v>30.1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>20.3</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="I2" s="1">
+        <v>13.09255319148936</v>
+      </c>
+      <c r="J2" s="1">
+        <v>22.4</v>
+      </c>
+      <c r="K2">
+        <v>73</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="E3" s="1">
+        <v>25.226717557251916</v>
+      </c>
+      <c r="F3" s="1">
+        <v>30.6</v>
+      </c>
+      <c r="G3" s="1">
+        <v>19.8</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="I3" s="1">
+        <v>10.282400000000003</v>
+      </c>
+      <c r="J3" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="K3">
+        <v>96</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>30.996666666666666</v>
+        <v>25.808633093525195</v>
       </c>
       <c r="F4" s="1">
-        <v>32.4</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+        <v>29.8</v>
+      </c>
+      <c r="G4" s="1">
+        <v>22.1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.8</v>
+      </c>
       <c r="I4" s="1">
-        <v>14.958333333333334</v>
+        <v>10.204511278195492</v>
       </c>
       <c r="J4" s="1">
-        <v>19.2</v>
+        <v>22.4</v>
+      </c>
+      <c r="K4">
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1045,29 +1079,34 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>30.272222222222215</v>
+        <v>26.570454545454549</v>
       </c>
       <c r="F5" s="1">
-        <v>31.4</v>
-      </c>
-      <c r="G5" s="1"/>
+        <v>29.7</v>
+      </c>
+      <c r="G5" s="1">
+        <v>23.5</v>
+      </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="I5" s="1">
-        <v>9.81666666666667</v>
+        <v>10.753174603174603</v>
       </c>
       <c r="J5" s="1">
-        <v>12.1</v>
+        <v>21.8</v>
+      </c>
+      <c r="K5">
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1075,29 +1114,34 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>29.690384615384623</v>
+        <v>25.81818181818182</v>
       </c>
       <c r="F6" s="1">
-        <v>31.5</v>
-      </c>
-      <c r="G6" s="1"/>
+        <v>29.8</v>
+      </c>
+      <c r="G6" s="1">
+        <v>22.9</v>
+      </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="I6" s="1">
-        <v>12.454761904761906</v>
+        <v>10.891666666666671</v>
       </c>
       <c r="J6" s="1">
-        <v>17.7</v>
+        <v>22</v>
+      </c>
+      <c r="K6">
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1105,34 +1149,34 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>28.464473684210521</v>
+        <v>27.00238095238095</v>
       </c>
       <c r="F7" s="1">
-        <v>32.700000000000003</v>
+        <v>30.2</v>
       </c>
       <c r="G7" s="1">
-        <v>23.1</v>
+        <v>24.3</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1">
-        <v>10.996923076923078</v>
+        <v>11.577777777777783</v>
       </c>
       <c r="J7" s="1">
-        <v>19.399999999999999</v>
+        <v>19.8</v>
       </c>
       <c r="K7" s="2">
-        <v>77.569230769230742</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1140,34 +1184,34 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D8">
         <v>7</v>
       </c>
       <c r="E8" s="1">
-        <v>26.221428571428572</v>
+        <v>26.526811594202908</v>
       </c>
       <c r="F8" s="1">
-        <v>30.8</v>
+        <v>29.6</v>
       </c>
       <c r="G8" s="1">
-        <v>22.4</v>
+        <v>23.9</v>
       </c>
       <c r="H8" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>9.2325396825396808</v>
+        <v>12.20152671755725</v>
       </c>
       <c r="J8" s="1">
         <v>22.2</v>
       </c>
       <c r="K8" s="2">
-        <v>107.92777777777779</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1175,34 +1219,34 @@
         <v>4</v>
       </c>
       <c r="B9">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <v>8</v>
       </c>
       <c r="E9" s="1">
-        <v>26.078787878787875</v>
+        <v>25.661111111111115</v>
       </c>
       <c r="F9" s="1">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="G9" s="1">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="H9" s="1">
-        <v>2.2000000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I9" s="1">
-        <v>7.4055555555555532</v>
+        <v>10.534285714285721</v>
       </c>
       <c r="J9" s="1">
-        <v>19.8</v>
+        <v>20.8</v>
       </c>
       <c r="K9" s="2">
-        <v>108.71349206349205</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1210,34 +1254,34 @@
         <v>4</v>
       </c>
       <c r="B10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C10">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D10">
         <v>9</v>
       </c>
       <c r="E10" s="1">
-        <v>26.142063492063492</v>
+        <v>26.490579710144939</v>
       </c>
       <c r="F10" s="1">
-        <v>31.2</v>
+        <v>30.3</v>
       </c>
       <c r="G10" s="1">
-        <v>22</v>
+        <v>23.1</v>
       </c>
       <c r="H10" s="1">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="I10" s="1">
-        <v>10.099186991869917</v>
+        <v>11.82826086956522</v>
       </c>
       <c r="J10" s="1">
-        <v>24.9</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="K10" s="2">
-        <v>114.87460317460314</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1245,34 +1289,34 @@
         <v>4</v>
       </c>
       <c r="B11">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C11">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D11">
         <v>10</v>
       </c>
       <c r="E11" s="1">
-        <v>25.638888888888889</v>
+        <v>26.680419580419571</v>
       </c>
       <c r="F11" s="1">
-        <v>30.7</v>
+        <v>29</v>
       </c>
       <c r="G11" s="1">
-        <v>22.3</v>
+        <v>25</v>
       </c>
       <c r="H11" s="1">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I11" s="1">
-        <v>9.0805555555555593</v>
+        <v>12.897902097902096</v>
       </c>
       <c r="J11" s="1">
-        <v>25.3</v>
+        <v>20.8</v>
       </c>
       <c r="K11" s="2">
-        <v>117.74014084507039</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1280,34 +1324,34 @@
         <v>4</v>
       </c>
       <c r="B12">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D12">
         <v>11</v>
       </c>
       <c r="E12" s="1">
-        <v>25.630555555555549</v>
+        <v>26.033057851239668</v>
       </c>
       <c r="F12" s="1">
-        <v>30.3</v>
+        <v>29.3</v>
       </c>
       <c r="G12" s="1">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="H12" s="1">
-        <v>9.4</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1">
-        <v>9.0777777777777828</v>
+        <v>10.252066115702485</v>
       </c>
       <c r="J12" s="1">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="K12" s="2">
-        <v>113.90416666666667</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1315,34 +1359,34 @@
         <v>4</v>
       </c>
       <c r="B13">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D13">
         <v>12</v>
       </c>
       <c r="E13" s="1">
-        <v>26.764341085271301</v>
+        <v>24.655303030303035</v>
       </c>
       <c r="F13" s="1">
-        <v>30.5</v>
+        <v>28.9</v>
       </c>
       <c r="G13" s="1">
-        <v>23.9</v>
+        <v>23.1</v>
       </c>
       <c r="H13" s="1">
-        <v>12.4</v>
+        <v>29.6</v>
       </c>
       <c r="I13" s="1">
-        <v>13.364285714285716</v>
+        <v>8.0189393939393963</v>
       </c>
       <c r="J13" s="1">
-        <v>25.5</v>
+        <v>26.2</v>
       </c>
       <c r="K13" s="2">
-        <v>98.599206349206341</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1350,34 +1394,34 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D14">
         <v>13</v>
       </c>
       <c r="E14" s="1">
-        <v>26.522463768115966</v>
+        <v>25.507575757575754</v>
       </c>
       <c r="F14" s="1">
         <v>29.2</v>
       </c>
       <c r="G14" s="1">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="H14" s="1">
-        <v>1</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="I14" s="1">
-        <v>13.146969696969705</v>
+        <v>8.0386363636363622</v>
       </c>
       <c r="J14" s="1">
-        <v>30.5</v>
+        <v>20.8</v>
       </c>
       <c r="K14" s="2">
-        <v>90.403030303030306</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1385,34 +1429,34 @@
         <v>4</v>
       </c>
       <c r="B15">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C15">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D15">
         <v>14</v>
       </c>
       <c r="E15" s="1">
-        <v>26.822857142857146</v>
+        <v>26.346153846153836</v>
       </c>
       <c r="F15" s="1">
-        <v>29.7</v>
+        <v>30.8</v>
       </c>
       <c r="G15" s="1">
-        <v>24.5</v>
+        <v>22.7</v>
       </c>
       <c r="H15" s="1">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="I15" s="1">
-        <v>11.907246376811599</v>
+        <v>7.9644927536231913</v>
       </c>
       <c r="J15" s="1">
-        <v>22.4</v>
+        <v>18.3</v>
       </c>
       <c r="K15" s="2">
-        <v>87.373188405797094</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1420,34 +1464,34 @@
         <v>4</v>
       </c>
       <c r="B16">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C16">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D16">
         <v>15</v>
       </c>
       <c r="E16" s="1">
-        <v>27.003787878787875</v>
+        <v>24.903007518797001</v>
       </c>
       <c r="F16" s="1">
-        <v>30.1</v>
+        <v>27.2</v>
       </c>
       <c r="G16" s="1">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="H16" s="1">
-        <v>0.4</v>
+        <v>28.8</v>
       </c>
       <c r="I16" s="1">
-        <v>10.888636363636364</v>
+        <v>9.9934782608695709</v>
       </c>
       <c r="J16" s="1">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="K16" s="2">
-        <v>83.0416666666667</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1455,34 +1499,34 @@
         <v>4</v>
       </c>
       <c r="B17">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C17">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D17">
         <v>16</v>
       </c>
       <c r="E17" s="1">
-        <v>26.907518796992481</v>
+        <v>26.017391304347818</v>
       </c>
       <c r="F17" s="1">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="G17" s="1">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="H17" s="1">
-        <v>1.8</v>
+        <v>26.8</v>
       </c>
       <c r="I17" s="1">
-        <v>9.8424000000000031</v>
+        <v>12.228260869565219</v>
       </c>
       <c r="J17" s="1">
-        <v>19.8</v>
+        <v>28.4</v>
       </c>
       <c r="K17" s="2">
-        <v>86.413492063492058</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1490,34 +1534,34 @@
         <v>4</v>
       </c>
       <c r="B18">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D18">
         <v>17</v>
       </c>
       <c r="E18" s="1">
-        <v>26.559420289855076</v>
+        <v>26.451449275362322</v>
       </c>
       <c r="F18" s="1">
-        <v>29.9</v>
+        <v>29.4</v>
       </c>
       <c r="G18" s="1">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="H18" s="1">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I18" s="1">
-        <v>10.010869565217396</v>
+        <v>12.521739130434783</v>
       </c>
       <c r="J18" s="1">
-        <v>20</v>
+        <v>23.7</v>
       </c>
       <c r="K18" s="2">
-        <v>88.616666666666646</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1525,34 +1569,34 @@
         <v>4</v>
       </c>
       <c r="B19">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C19">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D19">
         <v>18</v>
       </c>
       <c r="E19" s="1">
-        <v>25.510948905109494</v>
+        <v>26.450724637681148</v>
       </c>
       <c r="F19" s="1">
-        <v>28.8</v>
+        <v>29.6</v>
       </c>
       <c r="G19" s="1">
-        <v>22</v>
+        <v>23.9</v>
       </c>
       <c r="H19" s="1">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="I19" s="1">
-        <v>9.4999999999999947</v>
+        <v>10.842753623188411</v>
       </c>
       <c r="J19" s="1">
-        <v>24.9</v>
+        <v>19</v>
       </c>
       <c r="K19" s="2">
-        <v>93.706349206349131</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1560,34 +1604,34 @@
         <v>4</v>
       </c>
       <c r="B20">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D20">
         <v>19</v>
       </c>
       <c r="E20" s="1">
-        <v>25.225362318840585</v>
+        <v>25.529710144927535</v>
       </c>
       <c r="F20" s="1">
-        <v>29.5</v>
+        <v>28.7</v>
       </c>
       <c r="G20" s="1">
-        <v>20.8</v>
+        <v>23.4</v>
       </c>
       <c r="H20" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1">
-        <v>7.1492424242424262</v>
+        <v>7.6797101449275393</v>
       </c>
       <c r="J20" s="1">
-        <v>17.3</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="K20" s="2">
-        <v>99.713636363636397</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1595,34 +1639,34 @@
         <v>4</v>
       </c>
       <c r="B21">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D21">
         <v>20</v>
       </c>
       <c r="E21" s="1">
-        <v>25.783333333333335</v>
+        <v>25.952083333333334</v>
       </c>
       <c r="F21" s="1">
-        <v>30.2</v>
+        <v>29.2</v>
       </c>
       <c r="G21" s="1">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="H21" s="1">
-        <v>1</v>
+        <v>7.1</v>
       </c>
       <c r="I21" s="1">
-        <v>6.0086956521739152</v>
+        <v>7.5486111111111098</v>
       </c>
       <c r="J21" s="1">
-        <v>21.4</v>
+        <v>16.5</v>
       </c>
       <c r="K21" s="2">
-        <v>119.76884057971009</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1630,34 +1674,34 @@
         <v>4</v>
       </c>
       <c r="B22">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D22">
         <v>21</v>
       </c>
       <c r="E22" s="1">
-        <v>26.431060606060608</v>
+        <v>25.979861111111084</v>
       </c>
       <c r="F22" s="1">
-        <v>30.6</v>
+        <v>29.3</v>
       </c>
       <c r="G22" s="1">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="H22" s="1">
-        <v>5.2</v>
+        <v>0.2</v>
       </c>
       <c r="I22" s="1">
-        <v>10.043939393939388</v>
+        <v>6.4069444444444459</v>
       </c>
       <c r="J22" s="1">
-        <v>22.2</v>
+        <v>17.5</v>
       </c>
       <c r="K22" s="2">
-        <v>111.66439393939388</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1665,34 +1709,34 @@
         <v>4</v>
       </c>
       <c r="B23">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C23">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D23">
         <v>22</v>
       </c>
       <c r="E23" s="1">
-        <v>26.003472222222232</v>
+        <v>26.622916666666683</v>
       </c>
       <c r="F23" s="1">
-        <v>30.6</v>
+        <v>32</v>
       </c>
       <c r="G23" s="1">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="H23" s="1">
-        <v>2.2000000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="I23" s="1">
-        <v>8.3993055555555625</v>
+        <v>7.629861111111115</v>
       </c>
       <c r="J23" s="1">
-        <v>19.8</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="K23" s="2">
-        <v>99.034027777777681</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1700,34 +1744,34 @@
         <v>4</v>
       </c>
       <c r="B24">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D24">
         <v>23</v>
       </c>
       <c r="E24" s="1">
-        <v>25.729861111111116</v>
+        <v>25.688888888888901</v>
       </c>
       <c r="F24" s="1">
-        <v>30.2</v>
+        <v>29.4</v>
       </c>
       <c r="G24" s="1">
-        <v>22.3</v>
+        <v>24.2</v>
       </c>
       <c r="H24" s="1">
-        <v>3</v>
+        <v>23.2</v>
       </c>
       <c r="I24" s="1">
-        <v>8.1493055555555642</v>
+        <v>8.7784722222222218</v>
       </c>
       <c r="J24" s="1">
-        <v>18.7</v>
+        <v>19.8</v>
       </c>
       <c r="K24" s="2">
-        <v>105.51319444444442</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1735,34 +1779,34 @@
         <v>4</v>
       </c>
       <c r="B25">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C25">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D25">
         <v>24</v>
       </c>
       <c r="E25" s="1">
-        <v>25.837878787878783</v>
+        <v>25.686805555555548</v>
       </c>
       <c r="F25" s="1">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="G25" s="1">
-        <v>22.3</v>
+        <v>23.4</v>
       </c>
       <c r="H25" s="1">
-        <v>0.6</v>
+        <v>10.8</v>
       </c>
       <c r="I25" s="1">
-        <v>5.9045454545454543</v>
+        <v>8.7701388888888872</v>
       </c>
       <c r="J25" s="1">
-        <v>14.2</v>
+        <v>22</v>
       </c>
       <c r="K25" s="2">
-        <v>105.69545454545454</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1770,34 +1814,34 @@
         <v>4</v>
       </c>
       <c r="B26">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C26">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D26">
         <v>25</v>
       </c>
       <c r="E26" s="1">
-        <v>25.567910447761186</v>
+        <v>26.755072463768119</v>
       </c>
       <c r="F26" s="1">
-        <v>29.1</v>
+        <v>31</v>
       </c>
       <c r="G26" s="1">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="H26" s="1">
-        <v>3.6</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="I26" s="1">
-        <v>5.9888888888888889</v>
+        <v>9.9605839416058384</v>
       </c>
       <c r="J26" s="1">
-        <v>14.2</v>
+        <v>20.6</v>
       </c>
       <c r="K26" s="2">
-        <v>110.90079365079362</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1805,34 +1849,34 @@
         <v>4</v>
       </c>
       <c r="B27">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C27">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D27">
         <v>26</v>
       </c>
       <c r="E27" s="1">
-        <v>26.516666666666673</v>
+        <v>25.33958333333333</v>
       </c>
       <c r="F27" s="1">
-        <v>30.5</v>
+        <v>29.2</v>
       </c>
       <c r="G27" s="1">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I27" s="1">
-        <v>7.9517543859649145</v>
+        <v>7.5604316546762629</v>
       </c>
       <c r="J27" s="1">
-        <v>16.100000000000001</v>
+        <v>21.2</v>
       </c>
       <c r="K27" s="2">
-        <v>102.96754385964911</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1840,34 +1884,34 @@
         <v>4</v>
       </c>
       <c r="B28">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D28">
         <v>27</v>
       </c>
       <c r="E28" s="1">
-        <v>26.592063492063478</v>
+        <v>25.390277777777765</v>
       </c>
       <c r="F28" s="1">
-        <v>30.9</v>
+        <v>28.6</v>
       </c>
       <c r="G28" s="1">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="H28" s="1">
-        <v>0.2</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="I28" s="1">
-        <v>9.8222222222222175</v>
+        <v>7.4687500000000018</v>
       </c>
       <c r="J28" s="1">
-        <v>21</v>
+        <v>23.5</v>
       </c>
       <c r="K28" s="2">
-        <v>94.95952380952383</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1875,34 +1919,34 @@
         <v>4</v>
       </c>
       <c r="B29">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C29">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D29">
         <v>28</v>
       </c>
       <c r="E29" s="1">
-        <v>25.884920634920636</v>
+        <v>25.407638888888904</v>
       </c>
       <c r="F29" s="1">
-        <v>29.9</v>
+        <v>28.5</v>
       </c>
       <c r="G29" s="1">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="H29" s="1">
-        <v>2.6</v>
+        <v>17.8</v>
       </c>
       <c r="I29" s="1">
-        <v>10.864166666666671</v>
+        <v>6.8680555555555545</v>
       </c>
       <c r="J29" s="1">
-        <v>37.299999999999997</v>
+        <v>19.8</v>
       </c>
       <c r="K29" s="2">
-        <v>106.26166666666667</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1910,34 +1954,34 @@
         <v>4</v>
       </c>
       <c r="B30">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C30">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D30">
         <v>29</v>
       </c>
       <c r="E30" s="1">
-        <v>26.903787878787888</v>
+        <v>25.593055555555548</v>
       </c>
       <c r="F30" s="1">
-        <v>29.8</v>
+        <v>29.3</v>
       </c>
       <c r="G30" s="1">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="H30" s="1">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="I30" s="1">
-        <v>13.782499999999992</v>
+        <v>6.447101449275368</v>
       </c>
       <c r="J30" s="1">
-        <v>25.1</v>
+        <v>16.5</v>
       </c>
       <c r="K30" s="2">
-        <v>80.752500000000055</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1945,34 +1989,34 @@
         <v>4</v>
       </c>
       <c r="B31">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C31">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D31">
         <v>30</v>
       </c>
       <c r="E31" s="1">
-        <v>25.970138888888886</v>
+        <v>26.449305555555565</v>
       </c>
       <c r="F31" s="1">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="G31" s="1">
-        <v>22.1</v>
+        <v>23.8</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I31" s="1">
-        <v>9.451449275362318</v>
+        <v>5.0881118881118903</v>
       </c>
       <c r="J31" s="1">
-        <v>23.3</v>
+        <v>15.2</v>
       </c>
       <c r="K31" s="2">
-        <v>104.60362318840579</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1980,34 +2024,34 @@
         <v>4</v>
       </c>
       <c r="B32">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C32">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D32">
         <v>31</v>
       </c>
       <c r="E32" s="1">
-        <v>25.738686131386874</v>
+        <v>25.775352112676057</v>
       </c>
       <c r="F32" s="1">
-        <v>30.6</v>
+        <v>29.9</v>
       </c>
       <c r="G32" s="1">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
       </c>
       <c r="I32" s="1">
-        <v>9.1708029197080254</v>
+        <v>7.7445255474452575</v>
       </c>
       <c r="J32" s="1">
-        <v>21.2</v>
+        <v>20</v>
       </c>
       <c r="K32" s="2">
-        <v>106.36788321167884</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -2015,34 +2059,34 @@
         <v>8</v>
       </c>
       <c r="B33">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C33">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33" s="1">
-        <v>30.31818181818182</v>
+        <v>25.049305555555559</v>
       </c>
       <c r="F33" s="1">
-        <v>36.1</v>
+        <v>28.9</v>
       </c>
       <c r="G33" s="1">
-        <v>26.4</v>
+        <v>21.6</v>
       </c>
       <c r="H33" s="1">
-        <v>4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="I33" s="1">
-        <v>3.4166666666666652</v>
+        <v>3.9787878787878799</v>
       </c>
       <c r="J33" s="1">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="K33" s="2">
-        <v>108.97142857142865</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -2050,34 +2094,34 @@
         <v>8</v>
       </c>
       <c r="B34">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C34">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D34">
         <v>2</v>
       </c>
       <c r="E34" s="1">
-        <v>30.227083333333344</v>
+        <v>25.293750000000003</v>
       </c>
       <c r="F34" s="1">
-        <v>38</v>
+        <v>29.7</v>
       </c>
       <c r="G34" s="1">
-        <v>26.3</v>
+        <v>21.1</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
       </c>
       <c r="I34" s="1">
-        <v>3.1180555555555558</v>
+        <v>4.1687499999999975</v>
       </c>
       <c r="J34" s="1">
-        <v>5.8</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="K34" s="2">
-        <v>125.16086956521737</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -2085,34 +2129,34 @@
         <v>8</v>
       </c>
       <c r="B35">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C35">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
       <c r="E35" s="1">
-        <v>30.654861111111117</v>
+        <v>24.779861111111114</v>
       </c>
       <c r="F35" s="1">
-        <v>36.700000000000003</v>
+        <v>28.2</v>
       </c>
       <c r="G35" s="1">
-        <v>27.1</v>
+        <v>21.2</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="I35" s="1">
-        <v>3.8027777777777754</v>
+        <v>3.8069930069930091</v>
       </c>
       <c r="J35" s="1">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="K35" s="2">
-        <v>108.83611111111108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -2120,34 +2164,34 @@
         <v>8</v>
       </c>
       <c r="B36">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C36">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36" s="1">
-        <v>30.293750000000014</v>
+        <v>25.950735294117656</v>
       </c>
       <c r="F36" s="1">
-        <v>35.6</v>
+        <v>29.3</v>
       </c>
       <c r="G36" s="1">
-        <v>27</v>
+        <v>22.8</v>
       </c>
       <c r="H36" s="1">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I36" s="1">
-        <v>3.5696969696969694</v>
+        <v>3.9031496062992126</v>
       </c>
       <c r="J36" s="1">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="K36" s="2">
-        <v>112.88906250000002</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -2155,34 +2199,34 @@
         <v>8</v>
       </c>
       <c r="B37">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C37">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D37">
         <v>5</v>
       </c>
       <c r="E37" s="1">
-        <v>30.527083333333337</v>
+        <v>25.975177304964557</v>
       </c>
       <c r="F37" s="1">
-        <v>35.9</v>
+        <v>29.5</v>
       </c>
       <c r="G37" s="1">
-        <v>27.2</v>
+        <v>24.2</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
       </c>
       <c r="I37" s="1">
-        <v>3.837301587301587</v>
+        <v>4.4547619047619023</v>
       </c>
       <c r="J37" s="1">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="K37" s="2">
-        <v>101.13015873015868</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -2190,34 +2234,34 @@
         <v>8</v>
       </c>
       <c r="B38">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C38">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D38">
         <v>6</v>
       </c>
       <c r="E38" s="1">
-        <v>30.234027777777783</v>
+        <v>26.436805555555583</v>
       </c>
       <c r="F38" s="1">
-        <v>36.799999999999997</v>
+        <v>29.7</v>
       </c>
       <c r="G38" s="1">
-        <v>26.6</v>
+        <v>23.8</v>
       </c>
       <c r="H38" s="1">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I38" s="1">
-        <v>3.6333333333333333</v>
+        <v>3.9398550724637693</v>
       </c>
       <c r="J38" s="1">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
       <c r="K38" s="2">
-        <v>111.93768115942029</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -2225,34 +2269,34 @@
         <v>8</v>
       </c>
       <c r="B39">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C39">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D39">
         <v>7</v>
       </c>
       <c r="E39" s="1">
-        <v>30.006521739130431</v>
+        <v>26.926086956521722</v>
       </c>
       <c r="F39" s="1">
-        <v>36.1</v>
+        <v>31.3</v>
       </c>
       <c r="G39" s="1">
-        <v>26.6</v>
+        <v>24.7</v>
       </c>
       <c r="H39" s="1">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I39" s="1">
-        <v>4.1037878787878785</v>
+        <v>4.5289855072463778</v>
       </c>
       <c r="J39" s="1">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="K39" s="2">
-        <v>104.27575757575758</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2260,34 +2304,34 @@
         <v>8</v>
       </c>
       <c r="B40">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C40">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D40">
         <v>8</v>
       </c>
       <c r="E40" s="1">
-        <v>29.686805555555551</v>
+        <v>26.170833333333338</v>
       </c>
       <c r="F40" s="1">
-        <v>36.200000000000003</v>
+        <v>29.1</v>
       </c>
       <c r="G40" s="1">
-        <v>26.5</v>
+        <v>23.7</v>
       </c>
       <c r="H40" s="1">
-        <v>3.4</v>
+        <v>0.2</v>
       </c>
       <c r="I40" s="1">
-        <v>3.725757575757576</v>
+        <v>4.0708333333333337</v>
       </c>
       <c r="J40" s="1">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="K40" s="2">
-        <v>113.57272727272725</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2295,34 +2339,34 @@
         <v>8</v>
       </c>
       <c r="B41">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C41">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D41">
         <v>9</v>
       </c>
       <c r="E41" s="1">
-        <v>29.811940298507459</v>
+        <v>26.188194444444445</v>
       </c>
       <c r="F41" s="1">
-        <v>36.1</v>
+        <v>30.1</v>
       </c>
       <c r="G41" s="1">
-        <v>26.5</v>
+        <v>23.1</v>
       </c>
       <c r="H41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="1">
-        <v>4.2041666666666648</v>
+        <v>4.2709219858156011</v>
       </c>
       <c r="J41" s="1">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="K41" s="2">
-        <v>112.25333333333339</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -2330,34 +2374,34 @@
         <v>8</v>
       </c>
       <c r="B42">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C42">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D42">
         <v>10</v>
       </c>
       <c r="E42" s="1">
-        <v>29.410416666666656</v>
+        <v>26.058695652173924</v>
       </c>
       <c r="F42" s="1">
-        <v>34.799999999999997</v>
+        <v>30</v>
       </c>
       <c r="G42" s="1">
-        <v>26.9</v>
+        <v>23.5</v>
       </c>
       <c r="H42" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I42" s="1">
-        <v>3.9381944444444446</v>
+        <v>4.511594202898551</v>
       </c>
       <c r="J42" s="1">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="K42" s="2">
-        <v>115.12916666666661</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2365,34 +2409,34 @@
         <v>8</v>
       </c>
       <c r="B43">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C43">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D43">
         <v>11</v>
       </c>
       <c r="E43" s="1">
-        <v>29.282608695652179</v>
+        <v>25.881944444444443</v>
       </c>
       <c r="F43" s="1">
-        <v>32.9</v>
+        <v>29.2</v>
       </c>
       <c r="G43" s="1">
-        <v>26.2</v>
+        <v>22.9</v>
       </c>
       <c r="H43" s="1">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I43" s="1">
-        <v>3.4916666666666671</v>
+        <v>3.8401515151515135</v>
       </c>
       <c r="J43" s="1">
-        <v>6.9</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="K43" s="2">
-        <v>114.69545454545458</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2400,34 +2444,34 @@
         <v>8</v>
       </c>
       <c r="B44">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C44">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D44">
         <v>12</v>
       </c>
       <c r="E44" s="1">
-        <v>30.236231884057979</v>
+        <v>25.311594202898561</v>
       </c>
       <c r="F44" s="1">
-        <v>35.5</v>
+        <v>28.6</v>
       </c>
       <c r="G44" s="1">
-        <v>27</v>
+        <v>23.7</v>
       </c>
       <c r="H44" s="1">
-        <v>15.4</v>
+        <v>9.6</v>
       </c>
       <c r="I44" s="1">
-        <v>4.6456521739130432</v>
+        <v>3.3231884057971013</v>
       </c>
       <c r="J44" s="1">
-        <v>9.1999999999999993</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="K44" s="2">
-        <v>102.09637681159424</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -2435,34 +2479,34 @@
         <v>8</v>
       </c>
       <c r="B45">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C45">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D45">
         <v>13</v>
       </c>
       <c r="E45" s="1">
-        <v>29.995833333333351</v>
+        <v>26.99513888888891</v>
       </c>
       <c r="F45" s="1">
-        <v>34.4</v>
+        <v>31.2</v>
       </c>
       <c r="G45" s="1">
-        <v>26.9</v>
+        <v>24.3</v>
       </c>
       <c r="H45" s="1">
-        <v>11.4</v>
+        <v>22.8</v>
       </c>
       <c r="I45" s="1">
-        <v>4.4212121212121218</v>
+        <v>3.9951388888888886</v>
       </c>
       <c r="J45" s="1">
-        <v>8.1999999999999993</v>
+        <v>8.9</v>
       </c>
       <c r="K45" s="2">
-        <v>100.46590909090911</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -2470,34 +2514,34 @@
         <v>8</v>
       </c>
       <c r="B46">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C46">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D46">
         <v>14</v>
       </c>
       <c r="E46" s="1">
-        <v>30.396527777777791</v>
+        <v>27.351388888888888</v>
       </c>
       <c r="F46" s="1">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="G46" s="1">
-        <v>26.8</v>
+        <v>25</v>
       </c>
       <c r="H46" s="1">
         <v>0.2</v>
       </c>
       <c r="I46" s="1">
-        <v>3.9696969696969715</v>
+        <v>3.3659722222222226</v>
       </c>
       <c r="J46" s="1">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="K46" s="2">
-        <v>103.44545454545451</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2505,34 +2549,34 @@
         <v>8</v>
       </c>
       <c r="B47">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C47">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D47">
         <v>15</v>
       </c>
       <c r="E47" s="1">
-        <v>30.586013986013988</v>
+        <v>26.735416666666676</v>
       </c>
       <c r="F47" s="1">
-        <v>35.1</v>
+        <v>30.6</v>
       </c>
       <c r="G47" s="1">
-        <v>27.8</v>
+        <v>25.3</v>
       </c>
       <c r="H47" s="1">
-        <v>3.2</v>
+        <v>13</v>
       </c>
       <c r="I47" s="1">
-        <v>3.8007299270072989</v>
+        <v>4.1043478260869559</v>
       </c>
       <c r="J47" s="1">
-        <v>8.1</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="K47" s="2">
-        <v>103.70145985401463</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -2540,34 +2584,34 @@
         <v>8</v>
       </c>
       <c r="B48">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C48">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D48">
         <v>16</v>
       </c>
       <c r="E48" s="1">
-        <v>30.91278195488723</v>
+        <v>26.907638888888876</v>
       </c>
       <c r="F48" s="1">
-        <v>35.700000000000003</v>
+        <v>30.5</v>
       </c>
       <c r="G48" s="1">
-        <v>27.9</v>
+        <v>24.5</v>
       </c>
       <c r="H48" s="1">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="I48" s="1">
-        <v>4.1049586776859517</v>
+        <v>4.5985507246376844</v>
       </c>
       <c r="J48" s="1">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="K48" s="2">
-        <v>95.070247933884289</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2575,34 +2619,34 @@
         <v>8</v>
       </c>
       <c r="B49">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C49">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D49">
         <v>17</v>
       </c>
       <c r="E49" s="1">
-        <v>30.10681818181817</v>
+        <v>26.470138888888904</v>
       </c>
       <c r="F49" s="1">
-        <v>35.200000000000003</v>
+        <v>30.9</v>
       </c>
       <c r="G49" s="1">
-        <v>26.1</v>
+        <v>23.7</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I49" s="1">
-        <v>3.8590909090909107</v>
+        <v>4.3944444444444422</v>
       </c>
       <c r="J49" s="1">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="K49" s="2">
-        <v>95.256060606060572</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2610,34 +2654,34 @@
         <v>8</v>
       </c>
       <c r="B50">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C50">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D50">
         <v>18</v>
       </c>
       <c r="E50" s="1">
-        <v>29.269852941176481</v>
+        <v>26.349999999999998</v>
       </c>
       <c r="F50" s="1">
-        <v>33.1</v>
+        <v>30.1</v>
       </c>
       <c r="G50" s="1">
-        <v>26.4</v>
+        <v>23.5</v>
       </c>
       <c r="H50" s="1">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="I50" s="1">
-        <v>3.8119047619047635</v>
+        <v>4.0545454545454538</v>
       </c>
       <c r="J50" s="1">
         <v>8</v>
       </c>
       <c r="K50" s="2">
-        <v>99.998412698412707</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2645,34 +2689,34 @@
         <v>8</v>
       </c>
       <c r="B51">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C51">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D51">
         <v>19</v>
       </c>
       <c r="E51" s="1">
-        <v>29.276811594202886</v>
+        <v>25.858156028368807</v>
       </c>
       <c r="F51" s="1">
-        <v>34.799999999999997</v>
+        <v>28.9</v>
       </c>
       <c r="G51" s="1">
-        <v>25.2</v>
+        <v>20.3</v>
       </c>
       <c r="H51" s="1">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="I51" s="1">
-        <v>3.2484848484848503</v>
+        <v>3.6714285714285717</v>
       </c>
       <c r="J51" s="1">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="K51" s="2">
-        <v>97.099999999999966</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2680,34 +2724,34 @@
         <v>8</v>
       </c>
       <c r="B52">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C52">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D52">
         <v>20</v>
       </c>
       <c r="E52" s="1">
-        <v>29.736690647482032</v>
+        <v>25.217361111111114</v>
       </c>
       <c r="F52" s="1">
-        <v>34.700000000000003</v>
+        <v>27.9</v>
       </c>
       <c r="G52" s="1">
-        <v>25.6</v>
+        <v>22.5</v>
       </c>
       <c r="H52" s="1">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I52" s="1">
-        <v>2.9188405797101442</v>
+        <v>3.056249999999999</v>
       </c>
       <c r="J52" s="1">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="K52" s="2">
-        <v>107.27753623188403</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2715,34 +2759,34 @@
         <v>8</v>
       </c>
       <c r="B53">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C53">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D53">
         <v>21</v>
       </c>
       <c r="E53" s="1">
-        <v>29.372222222222231</v>
+        <v>25.365972222222226</v>
       </c>
       <c r="F53" s="1">
-        <v>33.9</v>
+        <v>30</v>
       </c>
       <c r="G53" s="1">
-        <v>27.1</v>
+        <v>22.4</v>
       </c>
       <c r="H53" s="1">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I53" s="1">
-        <v>3.3985507246376803</v>
+        <v>3.0562500000000004</v>
       </c>
       <c r="J53" s="1">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="K53" s="2">
-        <v>104.30942028985507</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2750,34 +2794,34 @@
         <v>8</v>
       </c>
       <c r="B54">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C54">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D54">
         <v>22</v>
       </c>
       <c r="E54" s="1">
-        <v>29.922916666666652</v>
+        <v>26.707638888888866</v>
       </c>
       <c r="F54" s="1">
-        <v>35.1</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="G54" s="1">
-        <v>26.5</v>
+        <v>24.4</v>
       </c>
       <c r="H54" s="1">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="I54" s="1">
-        <v>3.7399999999999993</v>
+        <v>3.470833333333331</v>
       </c>
       <c r="J54" s="1">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="K54" s="2">
-        <v>99.741666666666674</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2785,34 +2829,34 @@
         <v>8</v>
       </c>
       <c r="B55">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C55">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D55">
         <v>23</v>
       </c>
       <c r="E55" s="1">
-        <v>30.083333333333332</v>
+        <v>26.040972222222241</v>
       </c>
       <c r="F55" s="1">
-        <v>34.799999999999997</v>
+        <v>30.3</v>
       </c>
       <c r="G55" s="1">
-        <v>26.5</v>
+        <v>22.9</v>
       </c>
       <c r="H55" s="1">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I55" s="1">
-        <v>3.5361111111111105</v>
+        <v>3.7472222222222231</v>
       </c>
       <c r="J55" s="1">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="K55" s="2">
-        <v>100.87638888888887</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2820,34 +2864,34 @@
         <v>8</v>
       </c>
       <c r="B56">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C56">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D56">
         <v>24</v>
       </c>
       <c r="E56" s="1">
-        <v>29.751388888888886</v>
+        <v>26.795652173913023</v>
       </c>
       <c r="F56" s="1">
-        <v>35.1</v>
+        <v>29.8</v>
       </c>
       <c r="G56" s="1">
-        <v>26.8</v>
+        <v>24.6</v>
       </c>
       <c r="H56" s="1">
-        <v>1.2</v>
+        <v>13.8</v>
       </c>
       <c r="I56" s="1">
-        <v>3.0772727272727272</v>
+        <v>3.6253623188405788</v>
       </c>
       <c r="J56" s="1">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="K56" s="2">
-        <v>99.946969696969703</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2855,34 +2899,34 @@
         <v>8</v>
       </c>
       <c r="B57">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C57">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D57">
         <v>25</v>
       </c>
       <c r="E57" s="1">
-        <v>29.505555555555553</v>
+        <v>27.659420289855056</v>
       </c>
       <c r="F57" s="1">
-        <v>35.1</v>
+        <v>32.4</v>
       </c>
       <c r="G57" s="1">
-        <v>27.6</v>
+        <v>24.2</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="I57" s="1">
-        <v>3.1357142857142866</v>
+        <v>4.1840909090909104</v>
       </c>
       <c r="J57" s="1">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="K57" s="2">
-        <v>109.18211382113816</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2890,34 +2934,34 @@
         <v>8</v>
       </c>
       <c r="B58">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C58">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D58">
         <v>26</v>
       </c>
       <c r="E58" s="1">
-        <v>30.073188405797119</v>
+        <v>27.358333333333327</v>
       </c>
       <c r="F58" s="1">
-        <v>37.4</v>
+        <v>31.3</v>
       </c>
       <c r="G58" s="1">
-        <v>27.2</v>
+        <v>25</v>
       </c>
       <c r="H58" s="1">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="I58" s="1">
-        <v>3.1316666666666668</v>
+        <v>4.0311594202898542</v>
       </c>
       <c r="J58" s="1">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="K58" s="2">
-        <v>117.67666666666666</v>
+        <v>103</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2925,34 +2969,34 @@
         <v>8</v>
       </c>
       <c r="B59">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C59">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D59">
         <v>27</v>
       </c>
       <c r="E59" s="1">
-        <v>29.699270072992707</v>
+        <v>26.160869565217389</v>
       </c>
       <c r="F59" s="1">
-        <v>34.299999999999997</v>
+        <v>29.3</v>
       </c>
       <c r="G59" s="1">
-        <v>27.3</v>
+        <v>24.7</v>
       </c>
       <c r="H59" s="1">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="I59" s="1">
-        <v>3.8618320610687018</v>
+        <v>3.2992753623188404</v>
       </c>
       <c r="J59" s="1">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="K59" s="2">
-        <v>106.387786259542</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -2960,34 +3004,34 @@
         <v>8</v>
       </c>
       <c r="B60">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C60">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D60">
         <v>28</v>
       </c>
       <c r="E60" s="1">
-        <v>29.395683453237428</v>
+        <v>26.231250000000014</v>
       </c>
       <c r="F60" s="1">
-        <v>34.700000000000003</v>
+        <v>30.7</v>
       </c>
       <c r="G60" s="1">
-        <v>26.8</v>
+        <v>24.3</v>
       </c>
       <c r="H60" s="1">
-        <v>9.8000000000000007</v>
+        <v>53</v>
       </c>
       <c r="I60" s="1">
-        <v>4.0133858267716533</v>
+        <v>3.1243055555555546</v>
       </c>
       <c r="J60" s="1">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="K60" s="2">
-        <v>108.94251968503934</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -2995,34 +3039,34 @@
         <v>8</v>
       </c>
       <c r="B61">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C61">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D61">
         <v>29</v>
       </c>
       <c r="E61" s="1">
-        <v>30.33120567375887</v>
+        <v>27.363043478260881</v>
       </c>
       <c r="F61" s="1">
-        <v>34.1</v>
+        <v>31</v>
       </c>
       <c r="G61" s="1">
-        <v>26.8</v>
+        <v>25.7</v>
       </c>
       <c r="H61" s="1">
-        <v>2.6</v>
+        <v>15.6</v>
       </c>
       <c r="I61" s="1">
-        <v>4.794656488549621</v>
+        <v>3.4181159420289853</v>
       </c>
       <c r="J61" s="1">
-        <v>9.6</v>
+        <v>6.9</v>
       </c>
       <c r="K61" s="2">
-        <v>95.95158730158731</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -3030,34 +3074,34 @@
         <v>8</v>
       </c>
       <c r="B62">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C62">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D62">
         <v>30</v>
       </c>
       <c r="E62" s="1">
-        <v>29.684722222222238</v>
+        <v>27.463194444444454</v>
       </c>
       <c r="F62" s="1">
-        <v>35.4</v>
+        <v>31.3</v>
       </c>
       <c r="G62" s="1">
-        <v>24.9</v>
+        <v>25.6</v>
       </c>
       <c r="H62" s="1">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="I62" s="1">
-        <v>4.1456521739130459</v>
+        <v>2.9174242424242438</v>
       </c>
       <c r="J62" s="1">
-        <v>8.3000000000000007</v>
+        <v>6</v>
       </c>
       <c r="K62" s="2">
-        <v>100.72101449275357</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -3065,34 +3109,34 @@
         <v>8</v>
       </c>
       <c r="B63">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C63">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D63">
         <v>31</v>
       </c>
       <c r="E63" s="1">
-        <v>29.59225352112675</v>
+        <v>26.905633802816894</v>
       </c>
       <c r="F63" s="1">
-        <v>34.799999999999997</v>
+        <v>30.9</v>
       </c>
       <c r="G63" s="1">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="H63" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I63" s="1">
-        <v>3.8267175572519081</v>
+        <v>4.0042253521126758</v>
       </c>
       <c r="J63" s="1">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="K63" s="2">
-        <v>103.23129770992367</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -3100,34 +3144,34 @@
         <v>13</v>
       </c>
       <c r="B64">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C64">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D64">
         <v>1</v>
       </c>
       <c r="E64" s="1">
-        <v>27.425757575757576</v>
+        <v>26.102205882352941</v>
       </c>
       <c r="F64" s="1">
-        <v>35</v>
+        <v>30.8</v>
       </c>
       <c r="G64" s="1">
-        <v>23.4</v>
+        <v>21.6</v>
       </c>
       <c r="H64" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I64" s="1">
-        <v>2.0039682539682531</v>
+        <v>11.635714285714286</v>
       </c>
       <c r="J64" s="1">
-        <v>5.8</v>
+        <v>22.2</v>
       </c>
       <c r="K64" s="2">
-        <v>104.73439999999999</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -3135,34 +3179,34 @@
         <v>13</v>
       </c>
       <c r="B65">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C65">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D65">
         <v>2</v>
       </c>
       <c r="E65" s="1">
-        <v>26.733333333333327</v>
+        <v>25.393382352941178</v>
       </c>
       <c r="F65" s="1">
-        <v>34.299999999999997</v>
+        <v>30.3</v>
       </c>
       <c r="G65" s="1">
-        <v>22.5</v>
+        <v>21.2</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
       </c>
       <c r="I65" s="1">
-        <v>1.8652777777777787</v>
+        <v>9.7274809160305367</v>
       </c>
       <c r="J65" s="1">
-        <v>10</v>
+        <v>22.7</v>
       </c>
       <c r="K65" s="2">
-        <v>128.94513888888889</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -3170,34 +3214,34 @@
         <v>13</v>
       </c>
       <c r="B66">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C66">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D66">
         <v>3</v>
       </c>
       <c r="E66" s="1">
-        <v>27.573611111111102</v>
+        <v>26.062318840579707</v>
       </c>
       <c r="F66" s="1">
-        <v>34.299999999999997</v>
+        <v>30.1</v>
       </c>
       <c r="G66" s="1">
-        <v>23.4</v>
+        <v>22.6</v>
       </c>
       <c r="H66" s="1">
-        <v>8.6</v>
+        <v>3.2</v>
       </c>
       <c r="I66" s="1">
-        <v>2.3347222222222213</v>
+        <v>10.40909090909091</v>
       </c>
       <c r="J66" s="1">
-        <v>6.2</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="K66" s="2">
-        <v>94.133333333333283</v>
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -3205,34 +3249,34 @@
         <v>13</v>
       </c>
       <c r="B67">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C67">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D67">
         <v>4</v>
       </c>
       <c r="E67" s="1">
-        <v>26.943884892086331</v>
+        <v>26.846923076923076</v>
       </c>
       <c r="F67" s="1">
-        <v>32.4</v>
+        <v>30.6</v>
       </c>
       <c r="G67" s="1">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="H67" s="1">
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I67" s="1">
-        <v>2.2416058394160583</v>
+        <v>12.349586776859503</v>
       </c>
       <c r="J67" s="1">
-        <v>6.6</v>
+        <v>20.6</v>
       </c>
       <c r="K67" s="2">
-        <v>122.96131386861312</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -3240,34 +3284,34 @@
         <v>13</v>
       </c>
       <c r="B68">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C68">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D68">
         <v>5</v>
       </c>
       <c r="E68" s="1">
-        <v>27.687969924812034</v>
+        <v>26.347107438016526</v>
       </c>
       <c r="F68" s="1">
-        <v>34</v>
+        <v>30.2</v>
       </c>
       <c r="G68" s="1">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="H68" s="1">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="I68" s="1">
-        <v>2.5217391304347845</v>
+        <v>13.756140350877194</v>
       </c>
       <c r="J68" s="1">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="K68" s="2">
-        <v>99.806956521739096</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -3275,34 +3319,34 @@
         <v>13</v>
       </c>
       <c r="B69">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C69">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D69">
         <v>6</v>
       </c>
       <c r="E69" s="1">
-        <v>27.120289855072457</v>
+        <v>27.143801652892574</v>
       </c>
       <c r="F69" s="1">
-        <v>33.799999999999997</v>
+        <v>31</v>
       </c>
       <c r="G69" s="1">
-        <v>21.8</v>
+        <v>24.8</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I69" s="1">
-        <v>2.495238095238097</v>
+        <v>11.966666666666661</v>
       </c>
       <c r="J69" s="1">
-        <v>5.8</v>
+        <v>22.9</v>
       </c>
       <c r="K69" s="2">
-        <v>92.770634920634919</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -3310,34 +3354,34 @@
         <v>13</v>
       </c>
       <c r="B70">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C70">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D70">
         <v>7</v>
       </c>
       <c r="E70" s="1">
-        <v>26.721739130434781</v>
+        <v>27.137956204379574</v>
       </c>
       <c r="F70" s="1">
-        <v>33.299999999999997</v>
+        <v>30.4</v>
       </c>
       <c r="G70" s="1">
+        <v>24.2</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="I70" s="1">
+        <v>14.352272727272728</v>
+      </c>
+      <c r="J70" s="1">
         <v>21.8</v>
       </c>
-      <c r="H70" s="1">
-        <v>0</v>
-      </c>
-      <c r="I70" s="1">
-        <v>2.6431818181818185</v>
-      </c>
-      <c r="J70" s="1">
-        <v>7.7</v>
-      </c>
       <c r="K70" s="2">
-        <v>83.880303030303011</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -3345,34 +3389,34 @@
         <v>13</v>
       </c>
       <c r="B71">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C71">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D71">
         <v>8</v>
       </c>
       <c r="E71" s="1">
-        <v>26.886231884057953</v>
+        <v>26.599305555555546</v>
       </c>
       <c r="F71" s="1">
-        <v>31.9</v>
+        <v>31</v>
       </c>
       <c r="G71" s="1">
-        <v>23.4</v>
+        <v>24.4</v>
       </c>
       <c r="H71" s="1">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="I71" s="1">
-        <v>2.8090909090909104</v>
+        <v>12.332167832167832</v>
       </c>
       <c r="J71" s="1">
-        <v>7</v>
+        <v>23.3</v>
       </c>
       <c r="K71" s="2">
-        <v>76.671212121212093</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -3380,34 +3424,34 @@
         <v>13</v>
       </c>
       <c r="B72">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C72">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D72">
         <v>9</v>
       </c>
       <c r="E72" s="1">
-        <v>27.126984126984137</v>
+        <v>27.170588235294108</v>
       </c>
       <c r="F72" s="1">
-        <v>33.1</v>
+        <v>31.3</v>
       </c>
       <c r="G72" s="1">
-        <v>23</v>
+        <v>24.3</v>
       </c>
       <c r="H72" s="1">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="I72" s="1">
-        <v>3.1104000000000012</v>
+        <v>14.285606060606066</v>
       </c>
       <c r="J72" s="1">
-        <v>7.6</v>
+        <v>22.9</v>
       </c>
       <c r="K72" s="2">
-        <v>97.977599999999995</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -3415,34 +3459,34 @@
         <v>13</v>
       </c>
       <c r="B73">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C73">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D73">
         <v>10</v>
       </c>
       <c r="E73" s="1">
-        <v>26.895488721804512</v>
+        <v>27.033082706766912</v>
       </c>
       <c r="F73" s="1">
-        <v>34</v>
+        <v>30.1</v>
       </c>
       <c r="G73" s="1">
-        <v>23.3</v>
+        <v>25.1</v>
       </c>
       <c r="H73" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I73" s="1">
-        <v>3.6251968503937007</v>
+        <v>15.500000000000009</v>
       </c>
       <c r="J73" s="1">
-        <v>11.8</v>
+        <v>22</v>
       </c>
       <c r="K73" s="2">
-        <v>102.61889763779524</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -3450,34 +3494,34 @@
         <v>13</v>
       </c>
       <c r="B74">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C74">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D74">
         <v>11</v>
       </c>
       <c r="E74" s="1">
-        <v>26.050000000000011</v>
+        <v>26.938181818181832</v>
       </c>
       <c r="F74" s="1">
-        <v>31.3</v>
+        <v>30</v>
       </c>
       <c r="G74" s="1">
-        <v>22.8</v>
+        <v>25.3</v>
       </c>
       <c r="H74" s="1">
-        <v>9.6</v>
+        <v>0.2</v>
       </c>
       <c r="I74" s="1">
-        <v>2.8886363636363663</v>
+        <v>14.172549019607844</v>
       </c>
       <c r="J74" s="1">
-        <v>9.3000000000000007</v>
+        <v>24.1</v>
       </c>
       <c r="K74" s="2">
-        <v>89.282575757575728</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -3485,32 +3529,34 @@
         <v>13</v>
       </c>
       <c r="B75">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C75">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D75">
         <v>12</v>
       </c>
       <c r="E75" s="1">
-        <v>25.495138888888896</v>
+        <v>24.516799999999982</v>
       </c>
       <c r="F75" s="1">
-        <v>30.1</v>
+        <v>26.3</v>
       </c>
       <c r="G75" s="1">
-        <v>22.7</v>
-      </c>
-      <c r="H75" s="1"/>
+        <v>23.4</v>
+      </c>
+      <c r="H75" s="1">
+        <v>42</v>
+      </c>
       <c r="I75" s="1">
-        <v>2.3159420289855079</v>
+        <v>9.2243697478991624</v>
       </c>
       <c r="J75" s="1">
-        <v>7.3</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="K75" s="2">
-        <v>86.44347826086954</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -3518,34 +3564,34 @@
         <v>13</v>
       </c>
       <c r="B76">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C76">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D76">
         <v>13</v>
       </c>
       <c r="E76" s="1">
-        <v>25.71458333333333</v>
+        <v>25.904225352112686</v>
       </c>
       <c r="F76" s="1">
-        <v>31</v>
+        <v>29.9</v>
       </c>
       <c r="G76" s="1">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="H76" s="1">
-        <v>5.4</v>
+        <v>43.6</v>
       </c>
       <c r="I76" s="1">
-        <v>2.7037878787878777</v>
+        <v>9.7563492063492046</v>
       </c>
       <c r="J76" s="1">
-        <v>8</v>
+        <v>20.2</v>
       </c>
       <c r="K76" s="2">
-        <v>81.665891472868225</v>
+        <v>93</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -3553,34 +3599,34 @@
         <v>13</v>
       </c>
       <c r="B77">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C77">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D77">
         <v>14</v>
       </c>
       <c r="E77" s="1">
-        <v>25.315217391304326</v>
+        <v>26.922463768115936</v>
       </c>
       <c r="F77" s="1">
-        <v>29.7</v>
+        <v>30.7</v>
       </c>
       <c r="G77" s="1">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="H77" s="1">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="I77" s="1">
-        <v>2.082608695652175</v>
+        <v>9.1000000000000068</v>
       </c>
       <c r="J77" s="1">
-        <v>7</v>
+        <v>21.4</v>
       </c>
       <c r="K77" s="2">
-        <v>81.750724637681145</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -3588,34 +3634,34 @@
         <v>13</v>
       </c>
       <c r="B78">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C78">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D78">
         <v>15</v>
       </c>
       <c r="E78" s="1">
-        <v>24.929710144927544</v>
+        <v>25.268749999999997</v>
       </c>
       <c r="F78" s="1">
-        <v>29.5</v>
+        <v>28.1</v>
       </c>
       <c r="G78" s="1">
-        <v>22.8</v>
+        <v>24.1</v>
       </c>
       <c r="H78" s="1">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="I78" s="1">
-        <v>2.1036231884057974</v>
+        <v>10.935507246376815</v>
       </c>
       <c r="J78" s="1">
-        <v>7.5</v>
+        <v>21.6</v>
       </c>
       <c r="K78" s="2">
-        <v>112.59130434782611</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -3623,34 +3669,34 @@
         <v>13</v>
       </c>
       <c r="B79">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C79">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D79">
         <v>16</v>
       </c>
       <c r="E79" s="1">
-        <v>25.112499999999962</v>
+        <v>26.333333333333325</v>
       </c>
       <c r="F79" s="1">
-        <v>31.1</v>
+        <v>29.8</v>
       </c>
       <c r="G79" s="1">
-        <v>22.5</v>
+        <v>24.6</v>
       </c>
       <c r="H79" s="1">
-        <v>30.6</v>
+        <v>17.2</v>
       </c>
       <c r="I79" s="1">
-        <v>1.6499999999999988</v>
+        <v>12.655555555555555</v>
       </c>
       <c r="J79" s="1">
-        <v>5.2</v>
+        <v>22.9</v>
       </c>
       <c r="K79" s="2">
-        <v>137.60724637681156</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -3658,34 +3704,34 @@
         <v>13</v>
       </c>
       <c r="B80">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C80">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D80">
         <v>17</v>
       </c>
       <c r="E80" s="1">
-        <v>25.746376811594203</v>
+        <v>26.988888888888891</v>
       </c>
       <c r="F80" s="1">
-        <v>30.6</v>
+        <v>30</v>
       </c>
       <c r="G80" s="1">
-        <v>22.7</v>
+        <v>24.8</v>
       </c>
       <c r="H80" s="1">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I80" s="1">
-        <v>2.122727272727273</v>
+        <v>15.843333333333339</v>
       </c>
       <c r="J80" s="1">
-        <v>6.7</v>
+        <v>25.7</v>
       </c>
       <c r="K80" s="2">
-        <v>101.42424242424245</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -3693,34 +3739,34 @@
         <v>13</v>
       </c>
       <c r="B81">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C81">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D81">
         <v>18</v>
       </c>
       <c r="E81" s="1">
-        <v>25.606249999999992</v>
+        <v>26.956692913385805</v>
       </c>
       <c r="F81" s="1">
-        <v>30.7</v>
+        <v>30.1</v>
       </c>
       <c r="G81" s="1">
-        <v>22.7</v>
+        <v>24.9</v>
       </c>
       <c r="H81" s="1">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="I81" s="1">
-        <v>2.3510948905109501</v>
+        <v>13.049606299212604</v>
       </c>
       <c r="J81" s="1">
-        <v>7.4</v>
+        <v>20.6</v>
       </c>
       <c r="K81" s="2">
-        <v>86.796376811594186</v>
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -3728,34 +3774,34 @@
         <v>13</v>
       </c>
       <c r="B82">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C82">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D82">
         <v>19</v>
       </c>
       <c r="E82" s="1">
-        <v>26.077272727272732</v>
+        <v>26.254198473282464</v>
       </c>
       <c r="F82" s="1">
-        <v>30.9</v>
+        <v>28.9</v>
       </c>
       <c r="G82" s="1">
-        <v>22.2</v>
+        <v>23.9</v>
       </c>
       <c r="H82" s="1">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="I82" s="1">
-        <v>2.215873015873016</v>
+        <v>11.886259541984737</v>
       </c>
       <c r="J82" s="1">
-        <v>5.9</v>
+        <v>22</v>
       </c>
       <c r="K82" s="2">
-        <v>90.587301587301582</v>
+        <v>48</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -3763,34 +3809,34 @@
         <v>13</v>
       </c>
       <c r="B83">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C83">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D83">
         <v>20</v>
       </c>
       <c r="E83" s="1">
-        <v>24.184027777777757</v>
+        <v>26.436111111111099</v>
       </c>
       <c r="F83" s="1">
-        <v>28.4</v>
+        <v>29.4</v>
       </c>
       <c r="G83" s="1">
-        <v>20.9</v>
+        <v>23.8</v>
       </c>
       <c r="H83" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I83" s="1">
-        <v>1.7291666666666661</v>
+        <v>10.448611111111113</v>
       </c>
       <c r="J83" s="1">
-        <v>7</v>
+        <v>19.8</v>
       </c>
       <c r="K83" s="2">
-        <v>176.33333333333331</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -3798,34 +3844,34 @@
         <v>13</v>
       </c>
       <c r="B84">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C84">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D84">
         <v>21</v>
       </c>
       <c r="E84" s="1">
-        <v>25.581944444444435</v>
+        <v>26.028260869565226</v>
       </c>
       <c r="F84" s="1">
-        <v>30.6</v>
+        <v>28.8</v>
       </c>
       <c r="G84" s="1">
-        <v>23.4</v>
+        <v>24.4</v>
       </c>
       <c r="H84" s="1">
-        <v>47.2</v>
+        <v>0</v>
       </c>
       <c r="I84" s="1">
-        <v>2.0898550724637679</v>
+        <v>6.2804347826086939</v>
       </c>
       <c r="J84" s="1">
-        <v>6</v>
+        <v>13.4</v>
       </c>
       <c r="K84" s="2">
-        <v>115.68623188405797</v>
+        <v>73</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -3833,34 +3879,34 @@
         <v>13</v>
       </c>
       <c r="B85">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C85">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D85">
         <v>22</v>
       </c>
       <c r="E85" s="1">
-        <v>25.900704225352115</v>
+        <v>27.138194444444437</v>
       </c>
       <c r="F85" s="1">
-        <v>31.3</v>
+        <v>32</v>
       </c>
       <c r="G85" s="1">
-        <v>22.4</v>
+        <v>24.5</v>
       </c>
       <c r="H85" s="1">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="I85" s="1">
-        <v>2.6931818181818188</v>
+        <v>9.0597222222222271</v>
       </c>
       <c r="J85" s="1">
-        <v>7</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="K85" s="2">
-        <v>83.735606060606045</v>
+        <v>109</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -3868,34 +3914,34 @@
         <v>13</v>
       </c>
       <c r="B86">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C86">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D86">
         <v>23</v>
       </c>
       <c r="E86" s="1">
-        <v>26.315277777777801</v>
+        <v>26.814583333333342</v>
       </c>
       <c r="F86" s="1">
-        <v>31.7</v>
+        <v>30.9</v>
       </c>
       <c r="G86" s="1">
-        <v>23.7</v>
+        <v>25.2</v>
       </c>
       <c r="H86" s="1">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I86" s="1">
-        <v>2.2265734265734256</v>
+        <v>10.754861111111111</v>
       </c>
       <c r="J86" s="1">
-        <v>6.2</v>
+        <v>24.3</v>
       </c>
       <c r="K86" s="2">
-        <v>89.3715277777778</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -3903,34 +3949,34 @@
         <v>13</v>
       </c>
       <c r="B87">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C87">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D87">
         <v>24</v>
       </c>
       <c r="E87" s="1">
-        <v>25.360144927536226</v>
+        <v>25.811111111111114</v>
       </c>
       <c r="F87" s="1">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="G87" s="1">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="H87" s="1">
-        <v>1</v>
+        <v>17.2</v>
       </c>
       <c r="I87" s="1">
-        <v>1.9884057971014508</v>
+        <v>9.7676056338028161</v>
       </c>
       <c r="J87" s="1">
-        <v>7.8</v>
+        <v>25.1</v>
       </c>
       <c r="K87" s="2">
-        <v>181.70362318840583</v>
+        <v>104</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -3938,34 +3984,34 @@
         <v>13</v>
       </c>
       <c r="B88">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C88">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D88">
         <v>25</v>
       </c>
       <c r="E88" s="1">
-        <v>24.560294117647064</v>
+        <v>27.127338129496415</v>
       </c>
       <c r="F88" s="1">
-        <v>27.7</v>
+        <v>31.4</v>
       </c>
       <c r="G88" s="1">
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="H88" s="1">
-        <v>8</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="I88" s="1">
-        <v>1.8537878787878794</v>
+        <v>10.592805755395686</v>
       </c>
       <c r="J88" s="1">
-        <v>6.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="K88" s="2">
-        <v>162.40984848484854</v>
+        <v>111</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -3973,34 +4019,34 @@
         <v>13</v>
       </c>
       <c r="B89">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C89">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D89">
         <v>26</v>
       </c>
       <c r="E89" s="1">
-        <v>26.143478260869575</v>
+        <v>26.345985401459856</v>
       </c>
       <c r="F89" s="1">
-        <v>32.4</v>
+        <v>29.7</v>
       </c>
       <c r="G89" s="1">
-        <v>23.2</v>
+        <v>24.6</v>
       </c>
       <c r="H89" s="1">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="I89" s="1">
-        <v>1.8248000000000004</v>
+        <v>9.3297709923664183</v>
       </c>
       <c r="J89" s="1">
-        <v>7.7</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="K89" s="2">
-        <v>128.12519083969465</v>
+        <v>103</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -4008,34 +4054,34 @@
         <v>13</v>
       </c>
       <c r="B90">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C90">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D90">
         <v>27</v>
       </c>
       <c r="E90" s="1">
-        <v>26.627131782945717</v>
+        <v>25.747407407407398</v>
       </c>
       <c r="F90" s="1">
-        <v>32.1</v>
+        <v>29.1</v>
       </c>
       <c r="G90" s="1">
-        <v>24.2</v>
+        <v>23.6</v>
       </c>
       <c r="H90" s="1">
-        <v>2.8</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="I90" s="1">
-        <v>2.9294117647058822</v>
+        <v>8.7398496240601524</v>
       </c>
       <c r="J90" s="1">
-        <v>6.7</v>
+        <v>21.8</v>
       </c>
       <c r="K90" s="2">
-        <v>81.390756302521041</v>
+        <v>103</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -4043,34 +4089,34 @@
         <v>13</v>
       </c>
       <c r="B91">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C91">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D91">
         <v>28</v>
       </c>
       <c r="E91" s="1">
-        <v>25.66911764705883</v>
+        <v>25.806521739130417</v>
       </c>
       <c r="F91" s="1">
-        <v>31.9</v>
+        <v>28</v>
       </c>
       <c r="G91" s="1">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="H91" s="1">
-        <v>0</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="I91" s="1">
-        <v>2.1383333333333336</v>
+        <v>6.5058394160583983</v>
       </c>
       <c r="J91" s="1">
-        <v>7.7</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="K91" s="2">
-        <v>131.43500000000003</v>
+        <v>98</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -4078,34 +4124,34 @@
         <v>13</v>
       </c>
       <c r="B92">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C92">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D92">
         <v>29</v>
       </c>
       <c r="E92" s="1">
-        <v>25.539416058394146</v>
+        <v>26.154887218045115</v>
       </c>
       <c r="F92" s="1">
-        <v>29.8</v>
+        <v>29.2</v>
       </c>
       <c r="G92" s="1">
-        <v>22.9</v>
+        <v>24.6</v>
       </c>
       <c r="H92" s="1">
-        <v>20.6</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I92" s="1">
-        <v>2.4561983471074376</v>
+        <v>7.283458646616543</v>
       </c>
       <c r="J92" s="1">
-        <v>8.6999999999999993</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="K92" s="2">
-        <v>108.57874015748031</v>
+        <v>101</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -4113,34 +4159,34 @@
         <v>13</v>
       </c>
       <c r="B93">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C93">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D93">
         <v>30</v>
       </c>
       <c r="E93" s="1">
-        <v>25.083333333333325</v>
+        <v>26.532116788321169</v>
       </c>
       <c r="F93" s="1">
-        <v>31.9</v>
+        <v>29.5</v>
       </c>
       <c r="G93" s="1">
-        <v>20.9</v>
+        <v>24.5</v>
       </c>
       <c r="H93" s="1">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="I93" s="1">
-        <v>1.9288732394366228</v>
+        <v>6.0058394160583948</v>
       </c>
       <c r="J93" s="1">
-        <v>7.7</v>
+        <v>15.2</v>
       </c>
       <c r="K93" s="2">
-        <v>119.12357142857145</v>
+        <v>51</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -4148,1128 +4194,136 @@
         <v>13</v>
       </c>
       <c r="B94">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C94">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D94">
         <v>31</v>
       </c>
       <c r="E94" s="1">
-        <v>25.457746478873243</v>
+        <v>26.103521126760569</v>
       </c>
       <c r="F94" s="1">
-        <v>32</v>
+        <v>29.6</v>
       </c>
       <c r="G94" s="1">
-        <v>21.4</v>
+        <v>23.6</v>
       </c>
       <c r="H94" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I94" s="1">
-        <v>2.5761194029850749</v>
+        <v>11.192805755395687</v>
       </c>
       <c r="J94" s="1">
-        <v>6.7</v>
+        <v>22</v>
       </c>
       <c r="K94" s="2">
-        <v>110.62769230769227</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>14</v>
-      </c>
-      <c r="B95">
-        <v>2025</v>
-      </c>
-      <c r="C95">
-        <v>12</v>
-      </c>
-      <c r="D95">
-        <v>1</v>
-      </c>
-      <c r="E95" s="1">
-        <v>27.728099173553737</v>
-      </c>
-      <c r="F95" s="1">
-        <v>31.6</v>
-      </c>
-      <c r="G95" s="1">
-        <v>24.8</v>
-      </c>
-      <c r="H95" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="I95" s="1">
-        <v>8.6770642201834889</v>
-      </c>
-      <c r="J95" s="1">
-        <v>17.3</v>
-      </c>
-      <c r="K95" s="2">
-        <v>103.20183486238531</v>
-      </c>
+      <c r="E95" s="1"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>14</v>
-      </c>
-      <c r="B96">
-        <v>2025</v>
-      </c>
-      <c r="C96">
-        <v>12</v>
-      </c>
-      <c r="D96">
-        <v>2</v>
-      </c>
-      <c r="E96" s="1">
-        <v>26.648175182481758</v>
-      </c>
-      <c r="F96" s="1">
-        <v>31.5</v>
-      </c>
-      <c r="G96" s="1">
-        <v>23.9</v>
-      </c>
-      <c r="H96" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="I96" s="1">
-        <v>7.4717557251908442</v>
-      </c>
-      <c r="J96" s="1">
-        <v>17.7</v>
-      </c>
-      <c r="K96" s="2">
-        <v>105.02519083969463</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>14</v>
-      </c>
-      <c r="B97">
-        <v>2025</v>
-      </c>
-      <c r="C97">
-        <v>12</v>
-      </c>
-      <c r="D97">
-        <v>3</v>
-      </c>
-      <c r="E97" s="1">
-        <v>27.597916666666663</v>
-      </c>
-      <c r="F97" s="1">
-        <v>32.200000000000003</v>
-      </c>
-      <c r="G97" s="1">
-        <v>24</v>
-      </c>
-      <c r="H97" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="I97" s="1">
-        <v>9.6034722222222211</v>
-      </c>
-      <c r="J97" s="1">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="K97" s="2">
-        <v>113.24375000000005</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>14</v>
-      </c>
-      <c r="B98">
-        <v>2025</v>
-      </c>
-      <c r="C98">
-        <v>12</v>
-      </c>
-      <c r="D98">
-        <v>4</v>
-      </c>
-      <c r="E98" s="1">
-        <v>26.957638888888898</v>
-      </c>
-      <c r="F98" s="1">
-        <v>31.8</v>
-      </c>
-      <c r="G98" s="1">
-        <v>23.6</v>
-      </c>
-      <c r="H98" s="1">
-        <v>25</v>
-      </c>
-      <c r="I98" s="1">
-        <v>7.768840579710143</v>
-      </c>
-      <c r="J98" s="1">
-        <v>18.7</v>
-      </c>
-      <c r="K98" s="2">
-        <v>100.73478260869567</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>14</v>
-      </c>
-      <c r="B99">
-        <v>2025</v>
-      </c>
-      <c r="C99">
-        <v>12</v>
-      </c>
-      <c r="D99">
-        <v>5</v>
-      </c>
-      <c r="E99" s="1">
-        <v>27.344444444444434</v>
-      </c>
-      <c r="F99" s="1">
-        <v>31.8</v>
-      </c>
-      <c r="G99" s="1">
-        <v>24.2</v>
-      </c>
-      <c r="H99" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="I99" s="1">
-        <v>8.0322580645161334</v>
-      </c>
-      <c r="J99" s="1">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="K99" s="2">
-        <v>92.515833333333347</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>14</v>
-      </c>
-      <c r="B100">
-        <v>2025</v>
-      </c>
-      <c r="C100">
-        <v>12</v>
-      </c>
-      <c r="D100">
-        <v>6</v>
-      </c>
-      <c r="E100" s="1">
-        <v>27.377099236641225</v>
-      </c>
-      <c r="F100" s="1">
-        <v>32</v>
-      </c>
-      <c r="G100" s="1">
-        <v>24.2</v>
-      </c>
-      <c r="H100" s="1">
-        <v>0</v>
-      </c>
-      <c r="I100" s="1">
-        <v>9.7565217391304326</v>
-      </c>
-      <c r="J100" s="1">
-        <v>18.3</v>
-      </c>
-      <c r="K100" s="2">
-        <v>113.94086956521738</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>14</v>
-      </c>
-      <c r="B101">
-        <v>2025</v>
-      </c>
-      <c r="C101">
-        <v>12</v>
-      </c>
-      <c r="D101">
-        <v>7</v>
-      </c>
-      <c r="E101" s="1">
-        <v>27.019444444444449</v>
-      </c>
-      <c r="F101" s="1">
-        <v>31.3</v>
-      </c>
-      <c r="G101" s="1">
-        <v>24.6</v>
-      </c>
-      <c r="H101" s="1">
-        <v>0</v>
-      </c>
-      <c r="I101" s="1">
-        <v>10.613138686131391</v>
-      </c>
-      <c r="J101" s="1">
-        <v>21.6</v>
-      </c>
-      <c r="K101" s="2">
-        <v>110.34233576642335</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>14</v>
-      </c>
-      <c r="B102">
-        <v>2025</v>
-      </c>
-      <c r="C102">
-        <v>12</v>
-      </c>
-      <c r="D102">
-        <v>8</v>
-      </c>
-      <c r="E102" s="1">
-        <v>26.571074380165292</v>
-      </c>
-      <c r="F102" s="1">
-        <v>31.2</v>
-      </c>
-      <c r="G102" s="1">
-        <v>24.4</v>
-      </c>
-      <c r="H102" s="1">
-        <v>1</v>
-      </c>
-      <c r="I102" s="1">
-        <v>8.196694214876036</v>
-      </c>
-      <c r="J102" s="1">
-        <v>21.2</v>
-      </c>
-      <c r="K102" s="2">
-        <v>110.00991735537191</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>14</v>
-      </c>
-      <c r="B103">
-        <v>2025</v>
-      </c>
-      <c r="C103">
-        <v>12</v>
-      </c>
-      <c r="D103">
-        <v>9</v>
-      </c>
-      <c r="E103" s="1">
-        <v>26.458015267175579</v>
-      </c>
-      <c r="F103" s="1">
-        <v>30.7</v>
-      </c>
-      <c r="G103" s="1">
-        <v>23.8</v>
-      </c>
-      <c r="H103" s="1">
-        <v>8</v>
-      </c>
-      <c r="I103" s="1">
-        <v>9.9991228070175442</v>
-      </c>
-      <c r="J103" s="1">
-        <v>18.5</v>
-      </c>
-      <c r="K103" s="2">
-        <v>116.31228070175443</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>14</v>
-      </c>
-      <c r="B104">
-        <v>2025</v>
-      </c>
-      <c r="C104">
-        <v>12</v>
-      </c>
-      <c r="D104">
-        <v>10</v>
-      </c>
-      <c r="E104" s="1">
-        <v>26.097222222222225</v>
-      </c>
-      <c r="F104" s="1">
-        <v>29.2</v>
-      </c>
-      <c r="G104" s="1">
-        <v>23.9</v>
-      </c>
-      <c r="H104" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="I104" s="1">
-        <v>9.2458015267175622</v>
-      </c>
-      <c r="J104" s="1">
-        <v>17.899999999999999</v>
-      </c>
-      <c r="K104" s="2">
-        <v>120.28897637795274</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>14</v>
-      </c>
-      <c r="B105">
-        <v>2025</v>
-      </c>
-      <c r="C105">
-        <v>12</v>
-      </c>
-      <c r="D105">
-        <v>11</v>
-      </c>
-      <c r="E105" s="1">
-        <v>25.915873015873011</v>
-      </c>
-      <c r="F105" s="1">
-        <v>29.3</v>
-      </c>
-      <c r="G105" s="1">
-        <v>23.9</v>
-      </c>
-      <c r="H105" s="1">
-        <v>8.4</v>
-      </c>
-      <c r="I105" s="1">
-        <v>8.6973913043478337</v>
-      </c>
-      <c r="J105" s="1">
-        <v>21.6</v>
-      </c>
-      <c r="K105" s="2">
-        <v>123.09217391304347</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>14</v>
-      </c>
-      <c r="B106">
-        <v>2025</v>
-      </c>
-      <c r="C106">
-        <v>12</v>
-      </c>
-      <c r="D106">
-        <v>12</v>
-      </c>
-      <c r="E106" s="1">
-        <v>26.912878787878775</v>
-      </c>
-      <c r="F106" s="1">
-        <v>30.5</v>
-      </c>
-      <c r="G106" s="1">
-        <v>23.9</v>
-      </c>
-      <c r="H106" s="1">
-        <v>6.8</v>
-      </c>
-      <c r="I106" s="1">
-        <v>13.52442748091603</v>
-      </c>
-      <c r="J106" s="1">
-        <v>24.1</v>
-      </c>
-      <c r="K106" s="2">
-        <v>100.24885496183205</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>14</v>
-      </c>
-      <c r="B107">
-        <v>2025</v>
-      </c>
-      <c r="C107">
-        <v>12</v>
-      </c>
-      <c r="D107">
-        <v>13</v>
-      </c>
-      <c r="E107" s="1">
-        <v>26.609420289855073</v>
-      </c>
-      <c r="F107" s="1">
-        <v>29.7</v>
-      </c>
-      <c r="G107" s="1">
-        <v>23.8</v>
-      </c>
-      <c r="H107" s="1">
-        <v>16.8</v>
-      </c>
-      <c r="I107" s="1">
-        <v>13.26190476190477</v>
-      </c>
-      <c r="J107" s="1">
-        <v>24.1</v>
-      </c>
-      <c r="K107" s="2">
-        <v>92.480952380952388</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>14</v>
-      </c>
-      <c r="B108">
-        <v>2025</v>
-      </c>
-      <c r="C108">
-        <v>12</v>
-      </c>
-      <c r="D108">
-        <v>14</v>
-      </c>
-      <c r="E108" s="1">
-        <v>26.992125984251988</v>
-      </c>
-      <c r="F108" s="1">
-        <v>29.8</v>
-      </c>
-      <c r="G108" s="1">
-        <v>24.7</v>
-      </c>
-      <c r="H108" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="I108" s="1">
-        <v>14.138260869565213</v>
-      </c>
-      <c r="J108" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="K108" s="2">
-        <v>82.703478260869531</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>14</v>
-      </c>
-      <c r="B109">
-        <v>2025</v>
-      </c>
-      <c r="C109">
-        <v>12</v>
-      </c>
-      <c r="D109">
-        <v>15</v>
-      </c>
-      <c r="E109" s="1">
-        <v>27.247999999999987</v>
-      </c>
-      <c r="F109" s="1">
-        <v>30.8</v>
-      </c>
-      <c r="G109" s="1">
-        <v>24.6</v>
-      </c>
-      <c r="H109" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="I109" s="1">
-        <v>12.133620689655171</v>
-      </c>
-      <c r="J109" s="1">
-        <v>23.9</v>
-      </c>
-      <c r="K109" s="2">
-        <v>76.399159663865532</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>14</v>
-      </c>
-      <c r="B110">
-        <v>2025</v>
-      </c>
-      <c r="C110">
-        <v>12</v>
-      </c>
-      <c r="D110">
-        <v>16</v>
-      </c>
-      <c r="E110" s="1">
-        <v>27.429921259842537</v>
-      </c>
-      <c r="F110" s="1">
-        <v>30.8</v>
-      </c>
-      <c r="G110" s="1">
-        <v>24.8</v>
-      </c>
-      <c r="H110" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="I110" s="1">
-        <v>12.085826771653547</v>
-      </c>
-      <c r="J110" s="1">
-        <v>24.3</v>
-      </c>
-      <c r="K110" s="2">
-        <v>75.898425196850354</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>14</v>
-      </c>
-      <c r="B111">
-        <v>2025</v>
-      </c>
-      <c r="C111">
-        <v>12</v>
-      </c>
-      <c r="D111">
-        <v>17</v>
-      </c>
-      <c r="E111" s="1">
-        <v>27.101526717557249</v>
-      </c>
-      <c r="F111" s="1">
-        <v>30.5</v>
-      </c>
-      <c r="G111" s="1">
-        <v>24.2</v>
-      </c>
-      <c r="H111" s="1">
-        <v>0</v>
-      </c>
-      <c r="I111" s="1">
-        <v>11.651145038167947</v>
-      </c>
-      <c r="J111" s="1">
-        <v>20.399999999999999</v>
-      </c>
-      <c r="K111" s="2">
-        <v>81.170992366412193</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>14</v>
-      </c>
-      <c r="B112">
-        <v>2025</v>
-      </c>
-      <c r="C112">
-        <v>12</v>
-      </c>
-      <c r="D112">
-        <v>18</v>
-      </c>
-      <c r="E112" s="1">
-        <v>25.852898550724635</v>
-      </c>
-      <c r="F112" s="1">
-        <v>29.9</v>
-      </c>
-      <c r="G112" s="1">
-        <v>23.2</v>
-      </c>
-      <c r="H112" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="I112" s="1">
-        <v>11.394166666666665</v>
-      </c>
-      <c r="J112" s="1">
-        <v>23.7</v>
-      </c>
-      <c r="K112" s="2">
-        <v>79.800833333333372</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>14</v>
-      </c>
-      <c r="B113">
-        <v>2025</v>
-      </c>
-      <c r="C113">
-        <v>12</v>
-      </c>
-      <c r="D113">
-        <v>19</v>
-      </c>
-      <c r="E113" s="1">
-        <v>26.062121212121205</v>
-      </c>
-      <c r="F113" s="1">
-        <v>30</v>
-      </c>
-      <c r="G113" s="1">
-        <v>23</v>
-      </c>
-      <c r="H113" s="1">
-        <v>3</v>
-      </c>
-      <c r="I113" s="1">
-        <v>8.6090909090909129</v>
-      </c>
-      <c r="J113" s="1">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="K113" s="2">
-        <v>72.924793388429762</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>14</v>
-      </c>
-      <c r="B114">
-        <v>2025</v>
-      </c>
-      <c r="C114">
-        <v>12</v>
-      </c>
-      <c r="D114">
-        <v>20</v>
-      </c>
-      <c r="E114" s="1">
-        <v>26.485714285714277</v>
-      </c>
-      <c r="F114" s="1">
-        <v>30</v>
-      </c>
-      <c r="G114" s="1">
-        <v>23.9</v>
-      </c>
-      <c r="H114" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="I114" s="1">
-        <v>7.6863999999999981</v>
-      </c>
-      <c r="J114" s="1">
-        <v>16.3</v>
-      </c>
-      <c r="K114" s="2">
-        <v>92.026399999999995</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>14</v>
-      </c>
-      <c r="B115">
-        <v>2025</v>
-      </c>
-      <c r="C115">
-        <v>12</v>
-      </c>
-      <c r="D115">
-        <v>21</v>
-      </c>
-      <c r="E115" s="1">
-        <v>26.283458646616523</v>
-      </c>
-      <c r="F115" s="1">
-        <v>29.8</v>
-      </c>
-      <c r="G115" s="1">
-        <v>24.2</v>
-      </c>
-      <c r="H115" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="I115" s="1">
-        <v>9.7545454545454486</v>
-      </c>
-      <c r="J115" s="1">
-        <v>20</v>
-      </c>
-      <c r="K115" s="2">
-        <v>124.51239669421493</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>14</v>
-      </c>
-      <c r="B116">
-        <v>2025</v>
-      </c>
-      <c r="C116">
-        <v>12</v>
-      </c>
-      <c r="D116">
-        <v>22</v>
-      </c>
-      <c r="E116" s="1">
-        <v>26.465034965034956</v>
-      </c>
-      <c r="F116" s="1">
-        <v>30.5</v>
-      </c>
-      <c r="G116" s="1">
-        <v>23.7</v>
-      </c>
-      <c r="H116" s="1">
-        <v>3.4</v>
-      </c>
-      <c r="I116" s="1">
-        <v>10.386713286713293</v>
-      </c>
-      <c r="J116" s="1">
-        <v>19.8</v>
-      </c>
-      <c r="K116" s="2">
-        <v>87.922377622377596</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>14</v>
-      </c>
-      <c r="B117">
-        <v>2025</v>
-      </c>
-      <c r="C117">
-        <v>12</v>
-      </c>
-      <c r="D117">
-        <v>23</v>
-      </c>
-      <c r="E117" s="1">
-        <v>26.479166666666668</v>
-      </c>
-      <c r="F117" s="1">
-        <v>30.9</v>
-      </c>
-      <c r="G117" s="1">
-        <v>23.5</v>
-      </c>
-      <c r="H117" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="I117" s="1">
-        <v>9.41180555555556</v>
-      </c>
-      <c r="J117" s="1">
-        <v>20.399999999999999</v>
-      </c>
-      <c r="K117" s="2">
-        <v>86.087499999999963</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>14</v>
-      </c>
-      <c r="B118">
-        <v>2025</v>
-      </c>
-      <c r="C118">
-        <v>12</v>
-      </c>
-      <c r="D118">
-        <v>24</v>
-      </c>
-      <c r="E118" s="1">
-        <v>26.389583333333334</v>
-      </c>
-      <c r="F118" s="1">
-        <v>30.7</v>
-      </c>
-      <c r="G118" s="1">
-        <v>23.6</v>
-      </c>
-      <c r="H118" s="1">
-        <v>2</v>
-      </c>
-      <c r="I118" s="1">
-        <v>8.0326086956521738</v>
-      </c>
-      <c r="J118" s="1">
-        <v>17.3</v>
-      </c>
-      <c r="K118" s="2">
-        <v>85.350000000000009</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>14</v>
-      </c>
-      <c r="B119">
-        <v>2025</v>
-      </c>
-      <c r="C119">
-        <v>12</v>
-      </c>
-      <c r="D119">
-        <v>25</v>
-      </c>
-      <c r="E119" s="1">
-        <v>26.017424242424223</v>
-      </c>
-      <c r="F119" s="1">
-        <v>29.6</v>
-      </c>
-      <c r="G119" s="1">
-        <v>24.5</v>
-      </c>
-      <c r="H119" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="I119" s="1">
-        <v>7.7454545454545505</v>
-      </c>
-      <c r="J119" s="1">
-        <v>17.5</v>
-      </c>
-      <c r="K119" s="2">
-        <v>96.790909090909125</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>14</v>
-      </c>
-      <c r="B120">
-        <v>2025</v>
-      </c>
-      <c r="C120">
-        <v>12</v>
-      </c>
-      <c r="D120">
-        <v>26</v>
-      </c>
-      <c r="E120" s="1">
-        <v>26.675000000000008</v>
-      </c>
-      <c r="F120" s="1">
-        <v>31.3</v>
-      </c>
-      <c r="G120" s="1">
-        <v>24</v>
-      </c>
-      <c r="H120" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="I120" s="1">
-        <v>8.8950000000000049</v>
-      </c>
-      <c r="J120" s="1">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="K120" s="2">
-        <v>104.36166666666665</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>14</v>
-      </c>
-      <c r="B121">
-        <v>2025</v>
-      </c>
-      <c r="C121">
-        <v>12</v>
-      </c>
-      <c r="D121">
-        <v>27</v>
-      </c>
-      <c r="E121" s="1">
-        <v>26.260606060606055</v>
-      </c>
-      <c r="F121" s="1">
-        <v>29.3</v>
-      </c>
-      <c r="G121" s="1">
-        <v>24.3</v>
-      </c>
-      <c r="H121" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="I121" s="1">
-        <v>9.3849206349206398</v>
-      </c>
-      <c r="J121" s="1">
-        <v>27.4</v>
-      </c>
-      <c r="K121" s="2">
-        <v>86.437301587301562</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>14</v>
-      </c>
-      <c r="B122">
-        <v>2025</v>
-      </c>
-      <c r="C122">
-        <v>12</v>
-      </c>
-      <c r="D122">
-        <v>28</v>
-      </c>
-      <c r="E122" s="1">
-        <v>26.437190082644644</v>
-      </c>
-      <c r="F122" s="1">
-        <v>30.3</v>
-      </c>
-      <c r="G122" s="1">
-        <v>23.7</v>
-      </c>
-      <c r="H122" s="1">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="I122" s="1">
-        <v>11.092173913043487</v>
-      </c>
-      <c r="J122" s="1">
-        <v>24.1</v>
-      </c>
-      <c r="K122" s="2">
-        <v>102.35217391304347</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>14</v>
-      </c>
-      <c r="B123">
-        <v>2025</v>
-      </c>
-      <c r="C123">
-        <v>12</v>
-      </c>
-      <c r="D123">
-        <v>29</v>
-      </c>
-      <c r="E123" s="1">
-        <v>27.222900763358776</v>
-      </c>
-      <c r="F123" s="1">
-        <v>30.4</v>
-      </c>
-      <c r="G123" s="1">
-        <v>24.9</v>
-      </c>
-      <c r="H123" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="I123" s="1">
-        <v>15.269599999999997</v>
-      </c>
-      <c r="J123" s="1">
-        <v>25.5</v>
-      </c>
-      <c r="K123" s="2">
-        <v>81.100799999999978</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>14</v>
-      </c>
-      <c r="B124">
-        <v>2025</v>
-      </c>
-      <c r="C124">
-        <v>12</v>
-      </c>
-      <c r="D124">
-        <v>30</v>
-      </c>
-      <c r="E124" s="1">
-        <v>26.573611111111116</v>
-      </c>
-      <c r="F124" s="1">
-        <v>31</v>
-      </c>
-      <c r="G124" s="1">
-        <v>23.3</v>
-      </c>
-      <c r="H124" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="I124" s="1">
-        <v>10.66376811594203</v>
-      </c>
-      <c r="J124" s="1">
-        <v>25.3</v>
-      </c>
-      <c r="K124" s="2">
-        <v>79.662318840579758</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>14</v>
-      </c>
-      <c r="B125">
-        <v>2025</v>
-      </c>
-      <c r="C125">
-        <v>12</v>
-      </c>
-      <c r="D125">
-        <v>31</v>
-      </c>
-      <c r="E125" s="1">
-        <v>26.581538461538457</v>
-      </c>
-      <c r="F125" s="1">
-        <v>30.6</v>
-      </c>
-      <c r="G125" s="1">
-        <v>23.7</v>
-      </c>
-      <c r="H125" s="1">
-        <v>0</v>
-      </c>
-      <c r="I125" s="1">
-        <v>10.145384615384621</v>
-      </c>
-      <c r="J125" s="1">
-        <v>21</v>
-      </c>
-      <c r="K125" s="2">
-        <v>87.941732283464546</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E96" s="1"/>
+    </row>
+    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E97" s="1"/>
+    </row>
+    <row r="98" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E98" s="1"/>
+    </row>
+    <row r="99" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E99" s="1"/>
+    </row>
+    <row r="100" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E100" s="1"/>
+    </row>
+    <row r="101" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E101" s="1"/>
+    </row>
+    <row r="102" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E102" s="1"/>
+    </row>
+    <row r="103" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E103" s="1"/>
+    </row>
+    <row r="104" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E104" s="1"/>
+    </row>
+    <row r="105" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E105" s="1"/>
+    </row>
+    <row r="106" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E106" s="1"/>
+    </row>
+    <row r="107" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E107" s="1"/>
+    </row>
+    <row r="108" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E108" s="1"/>
+    </row>
+    <row r="109" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E109" s="1"/>
+    </row>
+    <row r="110" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E110" s="1"/>
+    </row>
+    <row r="111" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E111" s="1"/>
+    </row>
+    <row r="112" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E112" s="1"/>
+    </row>
+    <row r="113" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E113" s="1"/>
+    </row>
+    <row r="114" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E114" s="1"/>
+    </row>
+    <row r="115" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E115" s="1"/>
+    </row>
+    <row r="116" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E116" s="1"/>
+    </row>
+    <row r="117" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E117" s="1"/>
+    </row>
+    <row r="118" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E118" s="1"/>
+    </row>
+    <row r="119" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E119" s="1"/>
+    </row>
+    <row r="120" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E120" s="1"/>
+    </row>
+    <row r="121" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E121" s="1"/>
+    </row>
+    <row r="122" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E122" s="1"/>
+    </row>
+    <row r="123" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E123" s="1"/>
+    </row>
+    <row r="124" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E124" s="1"/>
+    </row>
+    <row r="125" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E125" s="1"/>
+    </row>
+    <row r="126" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E126" s="1"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E127" s="1"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E128" s="1"/>
     </row>
     <row r="129" spans="5:5" x14ac:dyDescent="0.25">
@@ -6285,99 +5339,6 @@
     </row>
     <row r="466" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E466" s="1"/>
-    </row>
-    <row r="467" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E467" s="1"/>
-    </row>
-    <row r="468" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E468" s="1"/>
-    </row>
-    <row r="469" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E469" s="1"/>
-    </row>
-    <row r="470" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E470" s="1"/>
-    </row>
-    <row r="471" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E471" s="1"/>
-    </row>
-    <row r="472" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E472" s="1"/>
-    </row>
-    <row r="473" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E473" s="1"/>
-    </row>
-    <row r="474" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E474" s="1"/>
-    </row>
-    <row r="475" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E475" s="1"/>
-    </row>
-    <row r="476" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E476" s="1"/>
-    </row>
-    <row r="477" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E477" s="1"/>
-    </row>
-    <row r="478" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E478" s="1"/>
-    </row>
-    <row r="479" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E479" s="1"/>
-    </row>
-    <row r="480" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E480" s="1"/>
-    </row>
-    <row r="481" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E481" s="1"/>
-    </row>
-    <row r="482" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E482" s="1"/>
-    </row>
-    <row r="483" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E483" s="1"/>
-    </row>
-    <row r="484" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E484" s="1"/>
-    </row>
-    <row r="485" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E485" s="1"/>
-    </row>
-    <row r="486" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E486" s="1"/>
-    </row>
-    <row r="487" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E487" s="1"/>
-    </row>
-    <row r="488" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E488" s="1"/>
-    </row>
-    <row r="489" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E489" s="1"/>
-    </row>
-    <row r="490" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E490" s="1"/>
-    </row>
-    <row r="491" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E491" s="1"/>
-    </row>
-    <row r="492" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E492" s="1"/>
-    </row>
-    <row r="493" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E493" s="1"/>
-    </row>
-    <row r="494" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E494" s="1"/>
-    </row>
-    <row r="495" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E495" s="1"/>
-    </row>
-    <row r="496" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E496" s="1"/>
-    </row>
-    <row r="497" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E497" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
